--- a/artfynd/A 34878-2022 artfynd.xlsx
+++ b/artfynd/A 34878-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34878-2022 artfynd.xlsx
+++ b/artfynd/A 34878-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104739346</v>
+        <v>104739402</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>395116.531239224</v>
+        <v>395321</v>
       </c>
       <c r="R2" t="n">
-        <v>6777111.903725225</v>
+        <v>6777075</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På tallstammarna.</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,22 +775,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>malou lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104739402</v>
+        <v>104739362</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>395320.8267853837</v>
+        <v>395275</v>
       </c>
       <c r="R3" t="n">
-        <v>6777075.36185901</v>
+        <v>6777112</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal gran. Rötad gran. 103 årsringar möjliga att räkna.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,44 +887,39 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>malou lundin</t>
+          <t>Uno Skog</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104739362</v>
+        <v>104739346</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>395274.4318265393</v>
+        <v>395117</v>
       </c>
       <c r="R4" t="n">
-        <v>6777111.561361011</v>
+        <v>6777112</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -979,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran. Rötad gran. 103 årsringar möjliga att räkna.</t>
+          <t>På tallstammarna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,16 +1009,11 @@
         <v>104739386</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1061,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>395272.8076611207</v>
+        <v>395273</v>
       </c>
       <c r="R5" t="n">
-        <v>6777105.806082297</v>
+        <v>6777106</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 34878-2022 artfynd.xlsx
+++ b/artfynd/A 34878-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739402</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739362</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739346</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,8 +1130,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104739386</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>